--- a/output_data/charts/M010000US01.xlsx
+++ b/output_data/charts/M010000US01.xlsx
@@ -161,32 +161,47 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$9</c:f>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="8">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="9">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -194,32 +209,47 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$9</c:f>
+              <c:f>Sheet1!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
+                  <c:v>2.700236503473063</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.810702860629819</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.749640772737755</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.749518834204014</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.819517696619896</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>2.890345649582837</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>3.075626053831262</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
                   <c:v>3.168561310577767</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="8">
                   <c:v>3.522446226485798</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="9">
                   <c:v>3.702724147051045</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
                   <c:v>3.957665254628713</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
                   <c:v>4.07029331955033</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
                   <c:v>3.978875786732258</c:v>
                 </c:pt>
               </c:numCache>
@@ -640,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -656,65 +686,105 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="B2" s="1">
-        <v>2.890345649582837</v>
+        <v>2.700236503473063</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="B3" s="1">
-        <v>3.075626053831262</v>
+        <v>2.810702860629819</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="B4" s="1">
-        <v>3.168561310577767</v>
+        <v>2.749640772737755</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="B5" s="1">
-        <v>3.522446226485798</v>
+        <v>2.749518834204014</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B6" s="1">
-        <v>3.702724147051045</v>
+        <v>2.819517696619896</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B7" s="1">
-        <v>3.957665254628713</v>
+        <v>2.890345649582837</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B8" s="1">
-        <v>4.07029331955033</v>
+        <v>3.075626053831262</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3.168561310577767</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3.522446226485798</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3.702724147051045</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3.957665254628713</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="1">
+        <v>4.07029331955033</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
         <v>2024</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B14" s="1">
         <v>3.978875786732258</v>
       </c>
     </row>
